--- a/artfynd/A 32078-2020 artfynd.xlsx
+++ b/artfynd/A 32078-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32078-2020 artfynd.xlsx
+++ b/artfynd/A 32078-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3262,6 +3262,1815 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120462358</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>658</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>514451</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7127678</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120462868</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>514602</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7127714</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120463229</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>514850</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7127772</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120461961</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>514430</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7127673</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120461934</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56524</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>514434</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7127664</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120463034</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>514728</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7127692</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120461794</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56524</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>514429</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7127717</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120461428</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>514400</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7127744</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120463301</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>514837</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7127775</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120463168</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>514781</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7127731</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120462913</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>514657</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7127716</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120462467</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>514483</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7127732</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120462652</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>514511</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7127705</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120462791</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>514585</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7127709</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120461843</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>514425</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7127721</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120461331</v>
+      </c>
+      <c r="B39" t="n">
+        <v>96891</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>514395</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7127799</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120462958</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>514701</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7127734</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32078-2020 artfynd.xlsx
+++ b/artfynd/A 32078-2020 artfynd.xlsx
@@ -3264,10 +3264,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120462358</v>
+        <v>120462958</v>
       </c>
       <c r="B24" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3280,21 +3280,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514451</v>
+        <v>514701</v>
       </c>
       <c r="R24" t="n">
-        <v>7127678</v>
+        <v>7127734</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3340,6 +3340,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,7 +3371,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120462868</v>
+        <v>120461961</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3400,21 +3405,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514602</v>
+        <v>514430</v>
       </c>
       <c r="R25" t="n">
-        <v>7127714</v>
+        <v>7127673</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack. Nyligen intorkad kåda</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3478,10 +3478,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120463229</v>
+        <v>120461934</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>56524</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3494,37 +3494,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514850</v>
+        <v>514434</v>
       </c>
       <c r="R26" t="n">
-        <v>7127772</v>
+        <v>7127664</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3580,10 +3585,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120461961</v>
+        <v>120463301</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3596,21 +3601,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3620,13 +3625,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514430</v>
+        <v>514837</v>
       </c>
       <c r="R27" t="n">
-        <v>7127673</v>
+        <v>7127775</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3656,11 +3661,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3687,10 +3687,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120461934</v>
+        <v>120461331</v>
       </c>
       <c r="B28" t="n">
-        <v>56524</v>
+        <v>96891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3699,46 +3699,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514434</v>
+        <v>514395</v>
       </c>
       <c r="R28" t="n">
-        <v>7127664</v>
+        <v>7127799</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3794,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120463034</v>
+        <v>120463229</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3810,21 +3805,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3834,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514728</v>
+        <v>514850</v>
       </c>
       <c r="R29" t="n">
-        <v>7127692</v>
+        <v>7127772</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3870,11 +3865,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3901,10 +3891,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120461794</v>
+        <v>120462913</v>
       </c>
       <c r="B30" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3917,16 +3907,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3935,24 +3925,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514429</v>
+        <v>514657</v>
       </c>
       <c r="R30" t="n">
-        <v>7127717</v>
+        <v>7127716</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3982,6 +3967,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4008,7 +3998,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120461428</v>
+        <v>120462868</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -4042,16 +4032,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514400</v>
+        <v>514602</v>
       </c>
       <c r="R31" t="n">
-        <v>7127744</v>
+        <v>7127714</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4088,7 +4083,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,10 +4110,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120463301</v>
+        <v>120462791</v>
       </c>
       <c r="B32" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4131,21 +4126,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4155,13 +4150,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514837</v>
+        <v>514585</v>
       </c>
       <c r="R32" t="n">
-        <v>7127775</v>
+        <v>7127709</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4191,6 +4186,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4329,7 +4329,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120462913</v>
+        <v>120462467</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4369,13 +4369,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514657</v>
+        <v>514483</v>
       </c>
       <c r="R34" t="n">
-        <v>7127716</v>
+        <v>7127732</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120462467</v>
+        <v>120461428</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4476,13 +4476,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514483</v>
+        <v>514400</v>
       </c>
       <c r="R35" t="n">
-        <v>7127732</v>
+        <v>7127744</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4543,10 +4543,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120462652</v>
+        <v>120461843</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>91879</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4555,46 +4555,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514511</v>
+        <v>514425</v>
       </c>
       <c r="R36" t="n">
-        <v>7127705</v>
+        <v>7127721</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4624,11 +4619,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4655,7 +4645,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120462791</v>
+        <v>120462652</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4689,19 +4679,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514585</v>
+        <v>514511</v>
       </c>
       <c r="R37" t="n">
-        <v>7127709</v>
+        <v>7127705</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4735,7 +4730,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4762,10 +4757,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120461843</v>
+        <v>120463034</v>
       </c>
       <c r="B38" t="n">
-        <v>91879</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4774,25 +4769,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4802,10 +4797,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514425</v>
+        <v>514728</v>
       </c>
       <c r="R38" t="n">
-        <v>7127721</v>
+        <v>7127692</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4838,6 +4833,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4864,10 +4864,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120461331</v>
+        <v>120461794</v>
       </c>
       <c r="B39" t="n">
-        <v>96891</v>
+        <v>56524</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4876,41 +4876,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514395</v>
+        <v>514429</v>
       </c>
       <c r="R39" t="n">
-        <v>7127799</v>
+        <v>7127717</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4966,10 +4971,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120462958</v>
+        <v>120462358</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4982,21 +4987,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5006,10 +5011,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514701</v>
+        <v>514451</v>
       </c>
       <c r="R40" t="n">
-        <v>7127734</v>
+        <v>7127678</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5042,11 +5047,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 32078-2020 artfynd.xlsx
+++ b/artfynd/A 32078-2020 artfynd.xlsx
@@ -3264,7 +3264,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120462958</v>
+        <v>120462868</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3298,16 +3298,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514701</v>
+        <v>514602</v>
       </c>
       <c r="R24" t="n">
-        <v>7127734</v>
+        <v>7127714</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3344,7 +3349,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3371,10 +3376,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120461961</v>
+        <v>120463229</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3387,21 +3392,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3411,10 +3416,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514430</v>
+        <v>514850</v>
       </c>
       <c r="R25" t="n">
-        <v>7127673</v>
+        <v>7127772</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3447,11 +3452,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3478,7 +3478,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120461934</v>
+        <v>120461794</v>
       </c>
       <c r="B26" t="n">
         <v>56524</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514434</v>
+        <v>514429</v>
       </c>
       <c r="R26" t="n">
-        <v>7127664</v>
+        <v>7127717</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3585,10 +3585,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120463301</v>
+        <v>120462791</v>
       </c>
       <c r="B27" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3625,13 +3625,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514837</v>
+        <v>514585</v>
       </c>
       <c r="R27" t="n">
-        <v>7127775</v>
+        <v>7127709</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3661,6 +3661,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3687,10 +3692,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120461331</v>
+        <v>120463168</v>
       </c>
       <c r="B28" t="n">
-        <v>96891</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3699,41 +3704,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514395</v>
+        <v>514781</v>
       </c>
       <c r="R28" t="n">
-        <v>7127799</v>
+        <v>7127731</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3763,6 +3773,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,10 +3804,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120463229</v>
+        <v>120462652</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3805,37 +3820,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514850</v>
+        <v>514511</v>
       </c>
       <c r="R29" t="n">
-        <v>7127772</v>
+        <v>7127705</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3865,6 +3885,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3891,10 +3916,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120462913</v>
+        <v>120461331</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>96891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3903,25 +3928,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3931,13 +3956,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514657</v>
+        <v>514395</v>
       </c>
       <c r="R30" t="n">
-        <v>7127716</v>
+        <v>7127799</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3967,11 +3992,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3998,10 +4018,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120462868</v>
+        <v>120461843</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>91879</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4010,43 +4030,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514602</v>
+        <v>514425</v>
       </c>
       <c r="R31" t="n">
-        <v>7127714</v>
+        <v>7127721</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4079,11 +4094,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4110,7 +4120,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120462791</v>
+        <v>120462958</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -4150,10 +4160,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514585</v>
+        <v>514701</v>
       </c>
       <c r="R32" t="n">
-        <v>7127709</v>
+        <v>7127734</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4217,10 +4227,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120463168</v>
+        <v>120462358</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4233,39 +4243,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514781</v>
+        <v>514451</v>
       </c>
       <c r="R33" t="n">
-        <v>7127731</v>
+        <v>7127678</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4298,11 +4303,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4436,10 +4436,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120461428</v>
+        <v>120461934</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>56524</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4452,16 +4452,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4470,19 +4470,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514400</v>
+        <v>514434</v>
       </c>
       <c r="R35" t="n">
-        <v>7127744</v>
+        <v>7127664</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4512,11 +4517,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4543,10 +4543,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120461843</v>
+        <v>120463034</v>
       </c>
       <c r="B36" t="n">
-        <v>91879</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4555,25 +4555,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514425</v>
+        <v>514728</v>
       </c>
       <c r="R36" t="n">
-        <v>7127721</v>
+        <v>7127692</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4619,6 +4619,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4645,7 +4650,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120462652</v>
+        <v>120461428</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4679,24 +4684,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514511</v>
+        <v>514400</v>
       </c>
       <c r="R37" t="n">
-        <v>7127705</v>
+        <v>7127744</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4757,7 +4757,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120463034</v>
+        <v>120461961</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514728</v>
+        <v>514430</v>
       </c>
       <c r="R38" t="n">
-        <v>7127692</v>
+        <v>7127673</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120461794</v>
+        <v>120462913</v>
       </c>
       <c r="B39" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4880,16 +4880,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4898,24 +4898,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514429</v>
+        <v>514657</v>
       </c>
       <c r="R39" t="n">
-        <v>7127717</v>
+        <v>7127716</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4945,6 +4940,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4971,10 +4971,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120462358</v>
+        <v>120463301</v>
       </c>
       <c r="B40" t="n">
-        <v>90864</v>
+        <v>79624</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4987,21 +4987,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5011,13 +5011,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514451</v>
+        <v>514837</v>
       </c>
       <c r="R40" t="n">
-        <v>7127678</v>
+        <v>7127775</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>

--- a/artfynd/A 32078-2020 artfynd.xlsx
+++ b/artfynd/A 32078-2020 artfynd.xlsx
@@ -3264,7 +3264,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120462868</v>
+        <v>120463034</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3298,21 +3298,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514602</v>
+        <v>514728</v>
       </c>
       <c r="R24" t="n">
-        <v>7127714</v>
+        <v>7127692</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3349,7 +3344,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack. Nyligen intorkad kåda</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3376,10 +3371,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120463229</v>
+        <v>120461331</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>96891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3388,25 +3383,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3416,13 +3411,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514850</v>
+        <v>514395</v>
       </c>
       <c r="R25" t="n">
-        <v>7127772</v>
+        <v>7127799</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3478,10 +3473,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120461794</v>
+        <v>120461961</v>
       </c>
       <c r="B26" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3494,16 +3489,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3512,24 +3507,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514429</v>
+        <v>514430</v>
       </c>
       <c r="R26" t="n">
-        <v>7127717</v>
+        <v>7127673</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3559,6 +3549,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3585,10 +3580,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120462791</v>
+        <v>120463229</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3601,21 +3596,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3625,10 +3620,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514585</v>
+        <v>514850</v>
       </c>
       <c r="R27" t="n">
-        <v>7127709</v>
+        <v>7127772</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3661,11 +3656,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3692,7 +3682,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120463168</v>
+        <v>120461428</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3726,21 +3716,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514781</v>
+        <v>514400</v>
       </c>
       <c r="R28" t="n">
-        <v>7127731</v>
+        <v>7127744</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3777,7 +3762,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3804,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120462652</v>
+        <v>120461934</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>56524</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3820,16 +3805,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3840,7 +3825,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3849,13 +3834,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514511</v>
+        <v>514434</v>
       </c>
       <c r="R29" t="n">
-        <v>7127705</v>
+        <v>7127664</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3885,11 +3870,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3916,10 +3896,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120461331</v>
+        <v>120462868</v>
       </c>
       <c r="B30" t="n">
-        <v>96891</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3928,41 +3908,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514395</v>
+        <v>514602</v>
       </c>
       <c r="R30" t="n">
-        <v>7127799</v>
+        <v>7127714</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3992,6 +3977,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4018,10 +4008,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120461843</v>
+        <v>120461794</v>
       </c>
       <c r="B31" t="n">
-        <v>91879</v>
+        <v>56524</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4030,41 +4020,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514425</v>
+        <v>514429</v>
       </c>
       <c r="R31" t="n">
-        <v>7127721</v>
+        <v>7127717</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4120,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120462958</v>
+        <v>120462358</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4136,21 +4131,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4160,10 +4155,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514701</v>
+        <v>514451</v>
       </c>
       <c r="R32" t="n">
-        <v>7127734</v>
+        <v>7127678</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4196,11 +4191,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4227,10 +4217,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120462358</v>
+        <v>120463301</v>
       </c>
       <c r="B33" t="n">
-        <v>90864</v>
+        <v>79624</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4243,21 +4233,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4267,13 +4257,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514451</v>
+        <v>514837</v>
       </c>
       <c r="R33" t="n">
-        <v>7127678</v>
+        <v>7127775</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4329,7 +4319,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120462467</v>
+        <v>120462958</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4369,13 +4359,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514483</v>
+        <v>514701</v>
       </c>
       <c r="R34" t="n">
-        <v>7127732</v>
+        <v>7127734</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,10 +4426,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120461934</v>
+        <v>120463168</v>
       </c>
       <c r="B35" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4452,16 +4442,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4472,7 +4462,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4481,13 +4471,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514434</v>
+        <v>514781</v>
       </c>
       <c r="R35" t="n">
-        <v>7127664</v>
+        <v>7127731</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4517,6 +4507,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4543,10 +4538,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120463034</v>
+        <v>120461843</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>91879</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4555,25 +4550,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4583,10 +4578,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514728</v>
+        <v>514425</v>
       </c>
       <c r="R36" t="n">
-        <v>7127692</v>
+        <v>7127721</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4619,11 +4614,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4650,7 +4640,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120461428</v>
+        <v>120462652</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4684,19 +4674,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514400</v>
+        <v>514511</v>
       </c>
       <c r="R37" t="n">
-        <v>7127744</v>
+        <v>7127705</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4730,7 +4725,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4757,7 +4752,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120461961</v>
+        <v>120462791</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4797,10 +4792,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514430</v>
+        <v>514585</v>
       </c>
       <c r="R38" t="n">
-        <v>7127673</v>
+        <v>7127709</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4971,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120463301</v>
+        <v>120462467</v>
       </c>
       <c r="B40" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4987,21 +4982,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5011,10 +5006,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514837</v>
+        <v>514483</v>
       </c>
       <c r="R40" t="n">
-        <v>7127775</v>
+        <v>7127732</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5047,6 +5042,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 32078-2020 artfynd.xlsx
+++ b/artfynd/A 32078-2020 artfynd.xlsx
@@ -3264,7 +3264,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120463034</v>
+        <v>120462791</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514728</v>
+        <v>514585</v>
       </c>
       <c r="R24" t="n">
-        <v>7127692</v>
+        <v>7127709</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3371,10 +3371,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120461331</v>
+        <v>120462868</v>
       </c>
       <c r="B25" t="n">
-        <v>96891</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3383,41 +3383,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514395</v>
+        <v>514602</v>
       </c>
       <c r="R25" t="n">
-        <v>7127799</v>
+        <v>7127714</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,6 +3452,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3473,7 +3483,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120461961</v>
+        <v>120461428</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3513,10 +3523,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514430</v>
+        <v>514400</v>
       </c>
       <c r="R26" t="n">
-        <v>7127673</v>
+        <v>7127744</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3553,7 +3563,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3580,10 +3590,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120463229</v>
+        <v>120461794</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>56524</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3596,37 +3606,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514850</v>
+        <v>514429</v>
       </c>
       <c r="R27" t="n">
-        <v>7127772</v>
+        <v>7127717</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3682,10 +3697,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120461428</v>
+        <v>120462358</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3698,21 +3713,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3722,10 +3737,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514400</v>
+        <v>514451</v>
       </c>
       <c r="R28" t="n">
-        <v>7127744</v>
+        <v>7127678</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3758,11 +3773,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,10 +3799,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120461934</v>
+        <v>120462958</v>
       </c>
       <c r="B29" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3805,16 +3815,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3823,24 +3833,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514434</v>
+        <v>514701</v>
       </c>
       <c r="R29" t="n">
-        <v>7127664</v>
+        <v>7127734</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3870,6 +3875,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3896,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120462868</v>
+        <v>120461331</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>96891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3908,46 +3918,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514602</v>
+        <v>514395</v>
       </c>
       <c r="R30" t="n">
-        <v>7127714</v>
+        <v>7127799</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3977,11 +3982,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4008,10 +4008,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120461794</v>
+        <v>120463229</v>
       </c>
       <c r="B31" t="n">
-        <v>56524</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4024,42 +4024,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514429</v>
+        <v>514850</v>
       </c>
       <c r="R31" t="n">
-        <v>7127717</v>
+        <v>7127772</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4115,10 +4110,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120462358</v>
+        <v>120463301</v>
       </c>
       <c r="B32" t="n">
-        <v>90864</v>
+        <v>79624</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4131,21 +4126,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4155,13 +4150,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514451</v>
+        <v>514837</v>
       </c>
       <c r="R32" t="n">
-        <v>7127678</v>
+        <v>7127775</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4217,10 +4212,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120463301</v>
+        <v>120462913</v>
       </c>
       <c r="B33" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4233,21 +4228,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4257,13 +4252,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514837</v>
+        <v>514657</v>
       </c>
       <c r="R33" t="n">
-        <v>7127775</v>
+        <v>7127716</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4293,6 +4288,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4319,7 +4319,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120462958</v>
+        <v>120462652</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4353,19 +4353,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514701</v>
+        <v>514511</v>
       </c>
       <c r="R34" t="n">
-        <v>7127734</v>
+        <v>7127705</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4399,7 +4404,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4426,7 +4431,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120463168</v>
+        <v>120463034</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4460,21 +4465,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514781</v>
+        <v>514728</v>
       </c>
       <c r="R35" t="n">
-        <v>7127731</v>
+        <v>7127692</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4538,10 +4538,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120461843</v>
+        <v>120462467</v>
       </c>
       <c r="B36" t="n">
-        <v>91879</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4550,25 +4550,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4578,13 +4578,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514425</v>
+        <v>514483</v>
       </c>
       <c r="R36" t="n">
-        <v>7127721</v>
+        <v>7127732</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4614,6 +4614,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4640,10 +4645,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120462652</v>
+        <v>120461934</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>56524</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4656,16 +4661,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4676,7 +4681,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4685,13 +4690,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514511</v>
+        <v>514434</v>
       </c>
       <c r="R37" t="n">
-        <v>7127705</v>
+        <v>7127664</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4721,11 +4726,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4752,10 +4752,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120462791</v>
+        <v>120461843</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>91879</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4764,25 +4764,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514585</v>
+        <v>514425</v>
       </c>
       <c r="R38" t="n">
-        <v>7127709</v>
+        <v>7127721</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4828,11 +4828,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,7 +4854,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120462913</v>
+        <v>120461961</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4899,10 +4894,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514657</v>
+        <v>514430</v>
       </c>
       <c r="R39" t="n">
-        <v>7127716</v>
+        <v>7127673</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4966,7 +4961,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120462467</v>
+        <v>120463168</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -5000,19 +4995,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514483</v>
+        <v>514781</v>
       </c>
       <c r="R40" t="n">
-        <v>7127732</v>
+        <v>7127731</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 32078-2020 artfynd.xlsx
+++ b/artfynd/A 32078-2020 artfynd.xlsx
@@ -4752,10 +4752,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120461843</v>
+        <v>120461961</v>
       </c>
       <c r="B38" t="n">
-        <v>91879</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4764,25 +4764,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514425</v>
+        <v>514430</v>
       </c>
       <c r="R38" t="n">
-        <v>7127721</v>
+        <v>7127673</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4828,6 +4828,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4854,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120461961</v>
+        <v>120461843</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>91879</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4866,25 +4871,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4894,10 +4899,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514430</v>
+        <v>514425</v>
       </c>
       <c r="R39" t="n">
-        <v>7127673</v>
+        <v>7127721</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4930,11 +4935,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
